--- a/Overpotnital/Air BP/75K/Edited/CN BM 1.5bp air_edited.xlsx
+++ b/Overpotnital/Air BP/75K/Edited/CN BM 1.5bp air_edited.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W284"/>
+  <dimension ref="A1:W144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="12.25" customWidth="1" style="1" min="10" max="10"/>
@@ -612,10 +612,10 @@
         <f>A4*B4</f>
         <v/>
       </c>
-      <c r="D4" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F4" s="0">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.55714</v>
+        <v>-0.532</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -684,10 +684,10 @@
         <f>A5*B5</f>
         <v/>
       </c>
-      <c r="D5" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F5" s="0">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.04315</v>
+        <v>-0.0384</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
@@ -756,10 +756,10 @@
         <f>A6*B6</f>
         <v/>
       </c>
-      <c r="D6" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F6" s="0">
@@ -820,10 +820,10 @@
         <f>A7*B7</f>
         <v/>
       </c>
-      <c r="D7" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F7" s="0">
@@ -884,10 +884,10 @@
         <f>A8*B8</f>
         <v/>
       </c>
-      <c r="D8" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F8" s="0">
@@ -948,10 +948,10 @@
         <f>A9*B9</f>
         <v/>
       </c>
-      <c r="D9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F9" s="0">
@@ -1012,10 +1012,10 @@
         <f>A10*B10</f>
         <v/>
       </c>
-      <c r="D10" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E10" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F10" s="0">
@@ -1076,10 +1076,10 @@
         <f>A11*B11</f>
         <v/>
       </c>
-      <c r="D11" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E11" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F11" s="0">
@@ -1140,10 +1140,10 @@
         <f>A12*B12</f>
         <v/>
       </c>
-      <c r="D12" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F12" s="0">
@@ -1204,10 +1204,10 @@
         <f>A13*B13</f>
         <v/>
       </c>
-      <c r="D13" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F13" s="0">
@@ -1268,10 +1268,10 @@
         <f>A14*B14</f>
         <v/>
       </c>
-      <c r="D14" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F14" s="0">
@@ -1332,10 +1332,10 @@
         <f>A15*B15</f>
         <v/>
       </c>
-      <c r="D15" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F15" s="0">
@@ -1396,10 +1396,10 @@
         <f>A16*B16</f>
         <v/>
       </c>
-      <c r="D16" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F16" s="0">
@@ -1460,10 +1460,10 @@
         <f>A17*B17</f>
         <v/>
       </c>
-      <c r="D17" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F17" s="0">
@@ -1524,10 +1524,10 @@
         <f>A18*B18</f>
         <v/>
       </c>
-      <c r="D18" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F18" s="0">
@@ -1588,10 +1588,10 @@
         <f>A19*B19</f>
         <v/>
       </c>
-      <c r="D19" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F19" s="0">
@@ -1652,10 +1652,10 @@
         <f>A20*B20</f>
         <v/>
       </c>
-      <c r="D20" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E20" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F20" s="0">
@@ -1716,10 +1716,10 @@
         <f>A21*B21</f>
         <v/>
       </c>
-      <c r="D21" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E21" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F21" s="0">
@@ -1780,10 +1780,10 @@
         <f>A22*B22</f>
         <v/>
       </c>
-      <c r="D22" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="D22" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E22" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F22" s="0">
@@ -1844,10 +1844,10 @@
         <f>A23*B23</f>
         <v/>
       </c>
-      <c r="D23" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="D23" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E23" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F23" s="0">
@@ -1908,10 +1908,10 @@
         <f>A24*B24</f>
         <v/>
       </c>
-      <c r="D24" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E24" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F24" s="0">
@@ -1972,10 +1972,10 @@
         <f>A25*B25</f>
         <v/>
       </c>
-      <c r="D25" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="D25" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E25" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F25" s="0">
@@ -2036,10 +2036,10 @@
         <f>A26*B26</f>
         <v/>
       </c>
-      <c r="D26" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="D26" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E26" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F26" s="0">
@@ -2100,10 +2100,10 @@
         <f>A27*B27</f>
         <v/>
       </c>
-      <c r="D27" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E27" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F27" s="0">
@@ -2164,10 +2164,10 @@
         <f>A28*B28</f>
         <v/>
       </c>
-      <c r="D28" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="D28" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E28" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F28" s="0">
@@ -2228,10 +2228,10 @@
         <f>A29*B29</f>
         <v/>
       </c>
-      <c r="D29" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E29" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F29" s="0">
@@ -2292,10 +2292,10 @@
         <f>A30*B30</f>
         <v/>
       </c>
-      <c r="D30" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E30" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F30" s="0">
@@ -2356,10 +2356,10 @@
         <f>A31*B31</f>
         <v/>
       </c>
-      <c r="D31" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E31" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F31" s="0">
@@ -2420,10 +2420,10 @@
         <f>A32*B32</f>
         <v/>
       </c>
-      <c r="D32" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="D32" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E32" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F32" s="0">
@@ -2484,10 +2484,10 @@
         <f>A33*B33</f>
         <v/>
       </c>
-      <c r="D33" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="D33" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E33" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F33" s="0">
@@ -2548,10 +2548,10 @@
         <f>A34*B34</f>
         <v/>
       </c>
-      <c r="D34" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="D34" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E34" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F34" s="0">
@@ -2612,10 +2612,10 @@
         <f>A35*B35</f>
         <v/>
       </c>
-      <c r="D35" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="D35" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E35" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F35" s="0">
@@ -2676,10 +2676,10 @@
         <f>A36*B36</f>
         <v/>
       </c>
-      <c r="D36" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="D36" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E36" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F36" s="0">
@@ -2740,10 +2740,10 @@
         <f>A37*B37</f>
         <v/>
       </c>
-      <c r="D37" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D37" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E37" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F37" s="0">
@@ -2804,10 +2804,10 @@
         <f>A38*B38</f>
         <v/>
       </c>
-      <c r="D38" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="D38" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E38" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F38" s="0">
@@ -2868,10 +2868,10 @@
         <f>A39*B39</f>
         <v/>
       </c>
-      <c r="D39" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="D39" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E39" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F39" s="0">
@@ -2932,10 +2932,10 @@
         <f>A40*B40</f>
         <v/>
       </c>
-      <c r="D40" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="D40" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E40" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F40" s="0">
@@ -2996,10 +2996,10 @@
         <f>A41*B41</f>
         <v/>
       </c>
-      <c r="D41" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="D41" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E41" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F41" s="0">
@@ -3060,10 +3060,10 @@
         <f>A42*B42</f>
         <v/>
       </c>
-      <c r="D42" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E42" t="n">
+      <c r="D42" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E42" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F42" s="0">
@@ -3124,10 +3124,10 @@
         <f>A43*B43</f>
         <v/>
       </c>
-      <c r="D43" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="D43" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E43" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F43" s="0">
@@ -3188,10 +3188,10 @@
         <f>A44*B44</f>
         <v/>
       </c>
-      <c r="D44" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="D44" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E44" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F44" s="0">
@@ -3252,10 +3252,10 @@
         <f>A45*B45</f>
         <v/>
       </c>
-      <c r="D45" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="D45" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E45" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F45" s="0">
@@ -3316,10 +3316,10 @@
         <f>A46*B46</f>
         <v/>
       </c>
-      <c r="D46" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E46" t="n">
+      <c r="D46" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E46" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F46" s="0">
@@ -3380,10 +3380,10 @@
         <f>A47*B47</f>
         <v/>
       </c>
-      <c r="D47" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="D47" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E47" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F47" s="0">
@@ -3444,10 +3444,10 @@
         <f>A48*B48</f>
         <v/>
       </c>
-      <c r="D48" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="D48" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E48" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F48" s="0">
@@ -3508,10 +3508,10 @@
         <f>A49*B49</f>
         <v/>
       </c>
-      <c r="D49" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E49" t="n">
+      <c r="D49" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E49" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F49" s="0">
@@ -3572,10 +3572,10 @@
         <f>A50*B50</f>
         <v/>
       </c>
-      <c r="D50" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E50" t="n">
+      <c r="D50" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E50" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F50" s="0">
@@ -3636,10 +3636,10 @@
         <f>A51*B51</f>
         <v/>
       </c>
-      <c r="D51" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E51" t="n">
+      <c r="D51" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E51" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F51" s="0">
@@ -3700,10 +3700,10 @@
         <f>A52*B52</f>
         <v/>
       </c>
-      <c r="D52" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="D52" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E52" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F52" s="0">
@@ -3764,10 +3764,10 @@
         <f>A53*B53</f>
         <v/>
       </c>
-      <c r="D53" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E53" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F53" s="0">
@@ -3828,10 +3828,10 @@
         <f>A54*B54</f>
         <v/>
       </c>
-      <c r="D54" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="D54" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E54" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F54" s="0">
@@ -3892,10 +3892,10 @@
         <f>A55*B55</f>
         <v/>
       </c>
-      <c r="D55" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="D55" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E55" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F55" s="0">
@@ -3956,10 +3956,10 @@
         <f>A56*B56</f>
         <v/>
       </c>
-      <c r="D56" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="D56" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E56" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F56" s="0">
@@ -4020,10 +4020,10 @@
         <f>A57*B57</f>
         <v/>
       </c>
-      <c r="D57" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="D57" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E57" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F57" s="0">
@@ -4084,10 +4084,10 @@
         <f>A58*B58</f>
         <v/>
       </c>
-      <c r="D58" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="D58" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E58" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F58" s="0">
@@ -4148,10 +4148,10 @@
         <f>A59*B59</f>
         <v/>
       </c>
-      <c r="D59" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="D59" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E59" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F59" s="0">
@@ -4212,10 +4212,10 @@
         <f>A60*B60</f>
         <v/>
       </c>
-      <c r="D60" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="D60" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E60" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F60" s="0">
@@ -4276,10 +4276,10 @@
         <f>A61*B61</f>
         <v/>
       </c>
-      <c r="D61" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E61" t="n">
+      <c r="D61" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E61" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F61" s="0">
@@ -4340,10 +4340,10 @@
         <f>A62*B62</f>
         <v/>
       </c>
-      <c r="D62" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E62" t="n">
+      <c r="D62" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E62" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F62" s="0">
@@ -4404,10 +4404,10 @@
         <f>A63*B63</f>
         <v/>
       </c>
-      <c r="D63" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E63" t="n">
+      <c r="D63" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E63" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F63" s="0">
@@ -4468,10 +4468,10 @@
         <f>A64*B64</f>
         <v/>
       </c>
-      <c r="D64" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E64" t="n">
+      <c r="D64" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E64" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F64" s="0">
@@ -4532,10 +4532,10 @@
         <f>A65*B65</f>
         <v/>
       </c>
-      <c r="D65" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E65" t="n">
+      <c r="D65" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E65" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F65" s="0">
@@ -4596,10 +4596,10 @@
         <f>A66*B66</f>
         <v/>
       </c>
-      <c r="D66" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E66" t="n">
+      <c r="D66" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E66" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F66" s="0">
@@ -4660,10 +4660,10 @@
         <f>A67*B67</f>
         <v/>
       </c>
-      <c r="D67" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="D67" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E67" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F67" s="0">
@@ -4724,10 +4724,10 @@
         <f>A68*B68</f>
         <v/>
       </c>
-      <c r="D68" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E68" t="n">
+      <c r="D68" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E68" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F68" s="0">
@@ -4788,10 +4788,10 @@
         <f>A69*B69</f>
         <v/>
       </c>
-      <c r="D69" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E69" t="n">
+      <c r="D69" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E69" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F69" s="0">
@@ -4852,10 +4852,10 @@
         <f>A70*B70</f>
         <v/>
       </c>
-      <c r="D70" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="D70" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E70" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F70" s="0">
@@ -4916,10 +4916,10 @@
         <f>A71*B71</f>
         <v/>
       </c>
-      <c r="D71" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="D71" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E71" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F71" s="0">
@@ -4980,10 +4980,10 @@
         <f>A72*B72</f>
         <v/>
       </c>
-      <c r="D72" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="D72" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E72" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F72" s="0">
@@ -5044,10 +5044,10 @@
         <f>A73*B73</f>
         <v/>
       </c>
-      <c r="D73" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="D73" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E73" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F73" s="0">
@@ -5108,10 +5108,10 @@
         <f>A74*B74</f>
         <v/>
       </c>
-      <c r="D74" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="D74" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E74" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F74" s="0">
@@ -5172,10 +5172,10 @@
         <f>A75*B75</f>
         <v/>
       </c>
-      <c r="D75" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E75" t="n">
+      <c r="D75" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E75" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F75" s="0">
@@ -5236,10 +5236,10 @@
         <f>A76*B76</f>
         <v/>
       </c>
-      <c r="D76" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="D76" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E76" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F76" s="0">
@@ -5300,10 +5300,10 @@
         <f>A77*B77</f>
         <v/>
       </c>
-      <c r="D77" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="D77" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E77" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F77" s="0">
@@ -5364,10 +5364,10 @@
         <f>A78*B78</f>
         <v/>
       </c>
-      <c r="D78" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="D78" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E78" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F78" s="0">
@@ -5428,10 +5428,10 @@
         <f>A79*B79</f>
         <v/>
       </c>
-      <c r="D79" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="D79" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E79" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F79" s="0">
@@ -5492,10 +5492,10 @@
         <f>A80*B80</f>
         <v/>
       </c>
-      <c r="D80" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="D80" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E80" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F80" s="0">
@@ -5556,10 +5556,10 @@
         <f>A81*B81</f>
         <v/>
       </c>
-      <c r="D81" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E81" t="n">
+      <c r="D81" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E81" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F81" s="0">
@@ -5620,10 +5620,10 @@
         <f>A82*B82</f>
         <v/>
       </c>
-      <c r="D82" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="D82" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E82" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F82" s="0">
@@ -5684,10 +5684,10 @@
         <f>A83*B83</f>
         <v/>
       </c>
-      <c r="D83" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E83" t="n">
+      <c r="D83" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E83" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F83" s="0">
@@ -5748,10 +5748,10 @@
         <f>A84*B84</f>
         <v/>
       </c>
-      <c r="D84" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="D84" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E84" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F84" s="0">
@@ -5812,10 +5812,10 @@
         <f>A85*B85</f>
         <v/>
       </c>
-      <c r="D85" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E85" t="n">
+      <c r="D85" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E85" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F85" s="0">
@@ -5876,10 +5876,10 @@
         <f>A86*B86</f>
         <v/>
       </c>
-      <c r="D86" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="D86" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E86" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F86" s="0">
@@ -5940,10 +5940,10 @@
         <f>A87*B87</f>
         <v/>
       </c>
-      <c r="D87" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="D87" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E87" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F87" s="0">
@@ -6004,10 +6004,10 @@
         <f>A88*B88</f>
         <v/>
       </c>
-      <c r="D88" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E88" t="n">
+      <c r="D88" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E88" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F88" s="0">
@@ -6068,10 +6068,10 @@
         <f>A89*B89</f>
         <v/>
       </c>
-      <c r="D89" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="D89" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E89" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F89" s="0">
@@ -6132,10 +6132,10 @@
         <f>A90*B90</f>
         <v/>
       </c>
-      <c r="D90" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E90" t="n">
+      <c r="D90" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E90" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F90" s="0">
@@ -6196,10 +6196,10 @@
         <f>A91*B91</f>
         <v/>
       </c>
-      <c r="D91" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E91" t="n">
+      <c r="D91" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E91" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F91" s="0">
@@ -6260,10 +6260,10 @@
         <f>A92*B92</f>
         <v/>
       </c>
-      <c r="D92" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E92" t="n">
+      <c r="D92" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E92" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F92" s="0">
@@ -6324,10 +6324,10 @@
         <f>A93*B93</f>
         <v/>
       </c>
-      <c r="D93" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E93" t="n">
+      <c r="D93" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E93" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F93" s="0">
@@ -6388,10 +6388,10 @@
         <f>A94*B94</f>
         <v/>
       </c>
-      <c r="D94" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E94" t="n">
+      <c r="D94" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E94" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F94" s="0">
@@ -6452,10 +6452,10 @@
         <f>A95*B95</f>
         <v/>
       </c>
-      <c r="D95" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E95" t="n">
+      <c r="D95" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E95" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F95" s="0">
@@ -6516,10 +6516,10 @@
         <f>A96*B96</f>
         <v/>
       </c>
-      <c r="D96" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E96" t="n">
+      <c r="D96" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E96" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F96" s="0">
@@ -6580,10 +6580,10 @@
         <f>A97*B97</f>
         <v/>
       </c>
-      <c r="D97" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E97" t="n">
+      <c r="D97" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E97" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F97" s="0">
@@ -6644,10 +6644,10 @@
         <f>A98*B98</f>
         <v/>
       </c>
-      <c r="D98" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E98" t="n">
+      <c r="D98" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E98" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F98" s="0">
@@ -6708,10 +6708,10 @@
         <f>A99*B99</f>
         <v/>
       </c>
-      <c r="D99" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E99" t="n">
+      <c r="D99" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E99" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F99" s="0">
@@ -6772,10 +6772,10 @@
         <f>A100*B100</f>
         <v/>
       </c>
-      <c r="D100" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E100" t="n">
+      <c r="D100" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E100" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F100" s="0">
@@ -6836,10 +6836,10 @@
         <f>A101*B101</f>
         <v/>
       </c>
-      <c r="D101" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E101" t="n">
+      <c r="D101" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E101" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F101" s="0">
@@ -6900,10 +6900,10 @@
         <f>A102*B102</f>
         <v/>
       </c>
-      <c r="D102" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E102" t="n">
+      <c r="D102" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E102" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F102" s="0">
@@ -6964,10 +6964,10 @@
         <f>A103*B103</f>
         <v/>
       </c>
-      <c r="D103" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E103" t="n">
+      <c r="D103" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E103" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F103" s="0">
@@ -7028,10 +7028,10 @@
         <f>A104*B104</f>
         <v/>
       </c>
-      <c r="D104" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="D104" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E104" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F104" s="0">
@@ -7092,10 +7092,10 @@
         <f>A105*B105</f>
         <v/>
       </c>
-      <c r="D105" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E105" t="n">
+      <c r="D105" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E105" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F105" s="0">
@@ -7156,10 +7156,10 @@
         <f>A106*B106</f>
         <v/>
       </c>
-      <c r="D106" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E106" t="n">
+      <c r="D106" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E106" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F106" s="0">
@@ -7220,10 +7220,10 @@
         <f>A107*B107</f>
         <v/>
       </c>
-      <c r="D107" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="D107" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E107" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F107" s="0">
@@ -7284,10 +7284,10 @@
         <f>A108*B108</f>
         <v/>
       </c>
-      <c r="D108" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="D108" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E108" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F108" s="0">
@@ -7348,10 +7348,10 @@
         <f>A109*B109</f>
         <v/>
       </c>
-      <c r="D109" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E109" t="n">
+      <c r="D109" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E109" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F109" s="0">
@@ -7412,10 +7412,10 @@
         <f>A110*B110</f>
         <v/>
       </c>
-      <c r="D110" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E110" t="n">
+      <c r="D110" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E110" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F110" s="0">
@@ -7476,10 +7476,10 @@
         <f>A111*B111</f>
         <v/>
       </c>
-      <c r="D111" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E111" t="n">
+      <c r="D111" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E111" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F111" s="0">
@@ -7540,10 +7540,10 @@
         <f>A112*B112</f>
         <v/>
       </c>
-      <c r="D112" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E112" t="n">
+      <c r="D112" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E112" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F112" s="0">
@@ -7604,10 +7604,10 @@
         <f>A113*B113</f>
         <v/>
       </c>
-      <c r="D113" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E113" t="n">
+      <c r="D113" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E113" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F113" s="0">
@@ -7668,10 +7668,10 @@
         <f>A114*B114</f>
         <v/>
       </c>
-      <c r="D114" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E114" t="n">
+      <c r="D114" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E114" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F114" s="0">
@@ -7732,10 +7732,10 @@
         <f>A115*B115</f>
         <v/>
       </c>
-      <c r="D115" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E115" t="n">
+      <c r="D115" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E115" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F115" s="0">
@@ -7796,10 +7796,10 @@
         <f>A116*B116</f>
         <v/>
       </c>
-      <c r="D116" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E116" t="n">
+      <c r="D116" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E116" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F116" s="0">
@@ -7860,10 +7860,10 @@
         <f>A117*B117</f>
         <v/>
       </c>
-      <c r="D117" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E117" t="n">
+      <c r="D117" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E117" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F117" s="0">
@@ -7924,10 +7924,10 @@
         <f>A118*B118</f>
         <v/>
       </c>
-      <c r="D118" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E118" t="n">
+      <c r="D118" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E118" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F118" s="0">
@@ -7988,10 +7988,10 @@
         <f>A119*B119</f>
         <v/>
       </c>
-      <c r="D119" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E119" t="n">
+      <c r="D119" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E119" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F119" s="0">
@@ -8052,10 +8052,10 @@
         <f>A120*B120</f>
         <v/>
       </c>
-      <c r="D120" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E120" t="n">
+      <c r="D120" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E120" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F120" s="0">
@@ -8116,10 +8116,10 @@
         <f>A121*B121</f>
         <v/>
       </c>
-      <c r="D121" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E121" t="n">
+      <c r="D121" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E121" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F121" s="0">
@@ -8180,10 +8180,10 @@
         <f>A122*B122</f>
         <v/>
       </c>
-      <c r="D122" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="D122" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E122" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F122" s="0">
@@ -8244,10 +8244,10 @@
         <f>A123*B123</f>
         <v/>
       </c>
-      <c r="D123" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E123" t="n">
+      <c r="D123" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E123" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F123" s="0">
@@ -8308,10 +8308,10 @@
         <f>A124*B124</f>
         <v/>
       </c>
-      <c r="D124" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E124" t="n">
+      <c r="D124" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E124" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F124" s="0">
@@ -8372,10 +8372,10 @@
         <f>A125*B125</f>
         <v/>
       </c>
-      <c r="D125" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E125" t="n">
+      <c r="D125" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E125" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F125" s="0">
@@ -8436,10 +8436,10 @@
         <f>A126*B126</f>
         <v/>
       </c>
-      <c r="D126" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E126" t="n">
+      <c r="D126" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E126" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F126" s="0">
@@ -8500,10 +8500,10 @@
         <f>A127*B127</f>
         <v/>
       </c>
-      <c r="D127" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E127" t="n">
+      <c r="D127" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E127" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F127" s="0">
@@ -8557,10 +8557,10 @@
         <f>A128*B128</f>
         <v/>
       </c>
-      <c r="D128" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E128" t="n">
+      <c r="D128" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E128" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F128" s="0">
@@ -8614,10 +8614,10 @@
         <f>A129*B129</f>
         <v/>
       </c>
-      <c r="D129" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E129" t="n">
+      <c r="D129" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E129" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F129" s="0">
@@ -8671,10 +8671,10 @@
         <f>A130*B130</f>
         <v/>
       </c>
-      <c r="D130" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E130" t="n">
+      <c r="D130" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E130" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F130" s="0">
@@ -8728,10 +8728,10 @@
         <f>A131*B131</f>
         <v/>
       </c>
-      <c r="D131" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E131" t="n">
+      <c r="D131" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E131" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F131" s="0">
@@ -8785,10 +8785,10 @@
         <f>A132*B132</f>
         <v/>
       </c>
-      <c r="D132" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E132" t="n">
+      <c r="D132" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E132" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F132" s="0">
@@ -8842,10 +8842,10 @@
         <f>A133*B133</f>
         <v/>
       </c>
-      <c r="D133" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E133" t="n">
+      <c r="D133" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E133" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F133" s="0">
@@ -8899,10 +8899,10 @@
         <f>A134*B134</f>
         <v/>
       </c>
-      <c r="D134" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E134" t="n">
+      <c r="D134" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E134" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F134" s="0">
@@ -8956,10 +8956,10 @@
         <f>A135*B135</f>
         <v/>
       </c>
-      <c r="D135" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E135" t="n">
+      <c r="D135" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E135" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F135" s="0">
@@ -9013,10 +9013,10 @@
         <f>A136*B136</f>
         <v/>
       </c>
-      <c r="D136" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E136" t="n">
+      <c r="D136" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E136" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F136" s="0">
@@ -9063,17 +9063,17 @@
       <c r="A137" s="0" t="n">
         <v>6.9426533</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="0" t="n">
         <v>0.27973</v>
       </c>
       <c r="C137" s="0">
         <f>A137*B137</f>
         <v/>
       </c>
-      <c r="D137" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E137" t="n">
+      <c r="D137" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E137" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F137" s="0">
@@ -9120,17 +9120,17 @@
       <c r="A138" s="0" t="n">
         <v>6.9940806</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="0" t="n">
         <v>0.27551</v>
       </c>
       <c r="C138" s="0">
         <f>A138*B138</f>
         <v/>
       </c>
-      <c r="D138" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E138" t="n">
+      <c r="D138" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E138" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F138" s="0">
@@ -9177,17 +9177,17 @@
       <c r="A139" s="0" t="n">
         <v>7.0444897</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="0" t="n">
         <v>0.27089</v>
       </c>
       <c r="C139" s="0">
         <f>A139*B139</f>
         <v/>
       </c>
-      <c r="D139" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E139" t="n">
+      <c r="D139" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E139" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F139" s="0">
@@ -9234,17 +9234,17 @@
       <c r="A140" s="0" t="n">
         <v>7.0954087</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="0" t="n">
         <v>0.26652</v>
       </c>
       <c r="C140" s="0">
         <f>A140*B140</f>
         <v/>
       </c>
-      <c r="D140" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E140" t="n">
+      <c r="D140" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E140" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F140" s="0">
@@ -9291,17 +9291,17 @@
       <c r="A141" s="0" t="n">
         <v>7.1468354</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" s="0" t="n">
         <v>0.26219</v>
       </c>
       <c r="C141" s="0">
         <f>A141*B141</f>
         <v/>
       </c>
-      <c r="D141" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E141" t="n">
+      <c r="D141" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E141" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F141" s="0">
@@ -9348,17 +9348,17 @@
       <c r="A142" s="0" t="n">
         <v>7.2002998</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" s="0" t="n">
         <v>0.25738</v>
       </c>
       <c r="C142" s="0">
         <f>A142*B142</f>
         <v/>
       </c>
-      <c r="D142" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E142" t="n">
+      <c r="D142" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E142" s="0" t="n">
         <v>0.015</v>
       </c>
       <c r="F142" s="0">
@@ -9406,10 +9406,10 @@
         <f>A143*B143</f>
         <v/>
       </c>
-      <c r="D143" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E143" t="n">
+      <c r="D143" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E143" s="0" t="n">
         <v>0.0171</v>
       </c>
       <c r="F143" s="0">
@@ -9457,10 +9457,10 @@
         <f>A144*B144</f>
         <v/>
       </c>
-      <c r="D144" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="E144" t="n">
+      <c r="D144" s="0" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="E144" s="0" t="n">
         <v>0.0171</v>
       </c>
       <c r="F144" s="0">
@@ -9503,146 +9503,6 @@
         <v/>
       </c>
     </row>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -11787,7 +11647,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="0" t="n">
         <v>1388.53066</v>
       </c>
       <c r="B134" s="0" t="n">
@@ -11803,7 +11663,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="0" t="n">
         <v>1398.81612</v>
       </c>
       <c r="B135" s="0" t="n">
@@ -11819,7 +11679,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="0" t="n">
         <v>1408.89794</v>
       </c>
       <c r="B136" s="0" t="n">
@@ -11835,7 +11695,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="0" t="n">
         <v>1419.08174</v>
       </c>
       <c r="B137" s="0" t="n">
@@ -11851,7 +11711,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="0" t="n">
         <v>1429.36708</v>
       </c>
       <c r="B138" s="0" t="n">
@@ -11867,7 +11727,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="0" t="n">
         <v>1440.05996</v>
       </c>
       <c r="B139" s="0" t="n">
@@ -11883,7 +11743,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" s="0" t="n">
         <v>1450.1418</v>
       </c>
       <c r="B140" s="0" t="n">
@@ -11899,7 +11759,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="0" t="n">
         <v>1452.99336</v>
       </c>
       <c r="B141" s="0" t="n">
